--- a/excel/ΣΑΠ-ΦΘ_FINAL_REPORT.xlsx
+++ b/excel/ΣΑΠ-ΦΘ_FINAL_REPORT.xlsx
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>46239.04032020104</v>
+        <v>46239.04214078294</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">

--- a/excel/ΣΑΠ-ΦΘ_FINAL_REPORT.xlsx
+++ b/excel/ΣΑΠ-ΦΘ_FINAL_REPORT.xlsx
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>46239.04214078294</v>
+        <v>46239.05291297977</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">

--- a/excel/ΣΑΠ-ΦΘ_FINAL_REPORT.xlsx
+++ b/excel/ΣΑΠ-ΦΘ_FINAL_REPORT.xlsx
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>46239.05291297977</v>
+        <v>46239.07508192052</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1">
